--- a/apiV4/PySR_LinearV2_annee_dyn/Validation_EPlus_VS_Opti.xlsx
+++ b/apiV4/PySR_LinearV2_annee_dyn/Validation_EPlus_VS_Opti.xlsx
@@ -599,13 +599,13 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>4.552996576929043</v>
+        <v>4.552996576929042</v>
       </c>
       <c r="C3">
         <v>5.267240387292256</v>
       </c>
       <c r="D3">
-        <v>0.7142438103632136</v>
+        <v>0.7142438103632145</v>
       </c>
       <c r="E3">
         <v>0.06062251406143262</v>
@@ -614,7 +614,7 @@
         <v>468.8042352903785</v>
       </c>
       <c r="G3">
-        <v>18.36099052208884</v>
+        <v>18.36099052208883</v>
       </c>
       <c r="H3">
         <v>32.32748999306379</v>
@@ -669,7 +669,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0.04328126285486597</v>
+        <v>0.04328126285486596</v>
       </c>
       <c r="C5">
         <v>0.6529173148950425</v>
@@ -710,7 +710,7 @@
         <v>0.3871256217130375</v>
       </c>
       <c r="D6">
-        <v>0.1761914265178415</v>
+        <v>0.1761914265178414</v>
       </c>
       <c r="E6">
         <v>0.1216365376869493</v>
@@ -722,7 +722,7 @@
         <v>67.05895313913496</v>
       </c>
       <c r="H6">
-        <v>7.591177942734005</v>
+        <v>7.591177942734004</v>
       </c>
       <c r="I6">
         <v>9.735314160004606</v>
@@ -809,7 +809,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-0.07052618599970853</v>
+        <v>-0.07052618599970857</v>
       </c>
       <c r="C9">
         <v>0.06929853922281422</v>
@@ -879,31 +879,31 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-0.04333480993134033</v>
+        <v>-0.04333480993134031</v>
       </c>
       <c r="C11">
         <v>-0.008481395413010842</v>
       </c>
       <c r="D11">
-        <v>0.03485341451832949</v>
+        <v>0.03485341451832946</v>
       </c>
       <c r="E11">
         <v>0.1661666758993949</v>
       </c>
       <c r="F11">
-        <v>993.2560810771757</v>
+        <v>993.256081077176</v>
       </c>
       <c r="G11">
-        <v>134.2193747585245</v>
+        <v>134.2193747585248</v>
       </c>
       <c r="H11">
-        <v>10.50099917635608</v>
+        <v>10.50099917635606</v>
       </c>
       <c r="I11">
         <v>12.22168950430474</v>
       </c>
       <c r="J11">
-        <v>437.54163234817</v>
+        <v>437.5416323481692</v>
       </c>
       <c r="K11">
         <v>509.237062679364</v>
